--- a/lcr_analyses/clustering/carriers/SEG_intermediate/cluster_summaries_hierarchical.xlsx
+++ b/lcr_analyses/clustering/carriers/SEG_intermediate/cluster_summaries_hierarchical.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4326,4 +4330,5538 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5612244897959183</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1671105193075899</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.85714285714285</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3386454183266932</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06374501992031872</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.03013698630136987</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7287671232876712</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2868525896414343</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1155378486055777</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4023904382470119</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>326</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.07712133227597145</v>
+      </c>
+      <c r="E4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05214723926380368</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.09815950920245399</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.343558282208589</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1226993865030675</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5061349693251533</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2269938650306748</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.02147239263803681</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1779141104294479</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.01840490797546012</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03987730061349693</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03680981595092025</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.006134969325153374</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.02760736196319018</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.03680981595092025</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2331288343558282</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.009202453987730062</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5766871165644172</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.006134969325153374</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.003067484662576687</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.006134969325153374</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.01226993865030675</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.02760736196319018</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4033613445378152</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5224974721941356</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1072627037392138</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.805564024390244</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.1084018801410106</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.0320525991370454</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.256066411238825</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>64</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>194</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>83</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2070949185043145</v>
+      </c>
+      <c r="E5" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0963855421686747</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.963855421686747</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04819277108433735</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.06024096385542169</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.2891566265060241</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.01204819277108434</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.850828729281768</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05882352941176469</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3725490196078431</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.4553571428571428</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2923076923076923</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>66</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>205</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05019685039370079</v>
+      </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06341463414634146</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1658536585365854</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5707317073170731</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02926829268292683</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.224390243902439</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.08292682926829269</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.00975609756097561</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1804878048780488</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01463414634146342</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.00975609756097561</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7886178861788617</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3714285714285714</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.2150537634408602</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1171875</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2225445843168109</v>
+      </c>
+      <c r="E7" t="n">
+        <v>27.07142857142857</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.7493985126859142</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.2669400699912511</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.01921478565179353</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.00752405949256343</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8559820647419072</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1486329833770779</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.2937335958005249</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.4423665791776028</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.1451006124234471</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2958005249343832</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1433962264150943</v>
+      </c>
+      <c r="E8" t="n">
+        <v>32.57142857142857</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.07456140350877194</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.02192982456140351</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1271929824561404</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.293859649122807</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.03947368421052632</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1798245614035088</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5612244897959183</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1671105193075899</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.85714285714285</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3386454183266932</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06374501992031872</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.03013698630136987</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7287671232876712</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2868525896414343</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1155378486055777</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4023904382470119</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.02563972160163322</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1840659340659341</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8516483516483516</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.6990950226244343</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.06512605042016806</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.2624434389140272</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.05952380952380952</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.05952380952380952</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.06203007518796992</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>316</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.07808582961546633</v>
+      </c>
+      <c r="E5" t="n">
+        <v>27.53571428571428</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05063291139240506</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1012658227848101</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.3449367088607595</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1265822784810127</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5031645569620253</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2341772151898734</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.02215189873417722</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1835443037974684</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.01582278481012658</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04113924050632911</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.03481012658227848</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02848101265822785</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.00949367088607595</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2405063291139241</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.00949367088607595</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5949367088607594</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.006329113924050633</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.01265822784810127</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02848101265822785</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4054054054054054</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1036109303838647</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8072944297082227</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.0320525991370454</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2644808743169399</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>193</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2070949185043145</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0963855421686747</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.963855421686747</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.04819277108433735</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.06024096385542169</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.2891566265060241</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01204819277108434</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.850828729281768</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.05882352941176469</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.3725490196078431</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4553571428571428</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2923076923076923</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>66</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>205</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.05019685039370079</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06341463414634146</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1658536585365854</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5707317073170731</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02926829268292683</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.224390243902439</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.08292682926829269</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.00975609756097561</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1804878048780488</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.01463414634146342</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.00975609756097561</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7886178861788617</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.3714285714285714</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.2150537634408602</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1171875</v>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2225445843168109</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27.07142857142857</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.7493985126859142</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.2669400699912511</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.01921478565179353</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.00752405949256343</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8559820647419072</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1486329833770779</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2937335958005249</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4423665791776028</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.1451006124234471</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2958005249343832</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1433962264150943</v>
+      </c>
+      <c r="E9" t="n">
+        <v>32.57142857142857</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.07456140350877194</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.02192982456140351</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1271929824561404</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.293859649122807</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.03947368421052632</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1798245614035088</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5612244897959183</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1671105193075899</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.85714285714285</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3386454183266932</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06374501992031872</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.03013698630136987</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7287671232876712</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2868525896414343</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1155378486055777</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4023904382470119</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.02563972160163322</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1840659340659341</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8516483516483516</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.6990950226244343</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.06512605042016806</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.2624434389140272</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.05952380952380952</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.05952380952380952</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.06203007518796992</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1741293478402276</v>
+      </c>
+      <c r="E5" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5170978293190605</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4846888280840659</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.09625231119328689</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.03491739969963528</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8310651275660785</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2506982796927569</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1025935844443151</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.346441947565543</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1344372166370984</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1341474064155557</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>310</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.07754868270332188</v>
+      </c>
+      <c r="E6" t="n">
+        <v>27.16666666666666</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0935483870967742</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3516129032258065</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1161290322580645</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5129032258064516</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2354838709677419</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01290322580645161</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1870967741935484</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02903225806451613</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.03548387096774194</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.003225806451612903</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.02903225806451613</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.00967741935483871</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2451612903225806</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.00967741935483871</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5870967741935483</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.00967741935483871</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.02903225806451613</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.4033613445378152</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1036109303838647</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8072944297082227</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.06098467945857503</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.01980392156862745</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.1062928600242033</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.03077651515151515</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.268543956043956</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>191</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2070949185043145</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0963855421686747</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.963855421686747</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04819277108433735</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.06024096385542169</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2891566265060241</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.01204819277108434</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.850828729281768</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.05882352941176469</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.3725490196078431</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.4553571428571428</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2923076923076923</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>66</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>205</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05019685039370079</v>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06341463414634146</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1658536585365854</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5707317073170731</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02926829268292683</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.224390243902439</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1463414634146341</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.08292682926829269</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.00975609756097561</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.004878048780487805</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1804878048780488</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01463414634146342</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.00975609756097561</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7886178861788617</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.3714285714285714</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.2150537634408602</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1171875</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2225445843168109</v>
+      </c>
+      <c r="E9" t="n">
+        <v>27.07142857142857</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.7493985126859142</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.2669400699912511</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.01921478565179353</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.00752405949256343</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.8559820647419072</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.1486329833770779</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.2937335958005249</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.4423665791776028</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.1451006124234471</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2958005249343832</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1433962264150943</v>
+      </c>
+      <c r="E10" t="n">
+        <v>32.57142857142857</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.07456140350877194</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.02192982456140351</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1271929824561404</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.293859649122807</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.03947368421052632</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1798245614035088</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5612244897959183</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1671105193075899</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.85714285714285</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3386454183266932</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06374501992031872</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.03013698630136987</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7287671232876712</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2868525896414343</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1155378486055777</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4023904382470119</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.02563972160163322</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1840659340659341</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.8516483516483516</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.6990950226244343</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.06512605042016806</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.2624434389140272</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.05952380952380952</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.05952380952380952</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.02380952380952381</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.06203007518796992</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1741293478402276</v>
+      </c>
+      <c r="E5" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5170978293190605</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4846888280840659</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.09625231119328689</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.03491739969963528</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.8310651275660785</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.2506982796927569</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1025935844443151</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.346441947565543</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1344372166370984</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1341474064155557</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>310</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.07754868270332188</v>
+      </c>
+      <c r="E6" t="n">
+        <v>27.16666666666666</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0935483870967742</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.3516129032258065</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1161290322580645</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5129032258064516</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2354838709677419</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01290322580645161</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1870967741935484</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02903225806451613</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.03548387096774194</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.003225806451612903</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.02903225806451613</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.00967741935483871</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2451612903225806</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.00967741935483871</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5870967741935483</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.00967741935483871</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.02903225806451613</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.4033613445378152</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1036109303838647</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8072944297082227</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.06098467945857503</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.01980392156862745</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.1062928600242033</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.03077651515151515</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.268543956043956</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>191</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2070949185043145</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0963855421686747</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.963855421686747</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.04819277108433735</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.108433734939759</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1807228915662651</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.03614457831325301</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.07228915662650602</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.06024096385542169</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2891566265060241</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.01204819277108434</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.850828729281768</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.2583333333333334</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.05882352941176469</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.3725490196078431</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.4553571428571428</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2923076923076923</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>66</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04608456710932353</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1285714285714286</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1857142857142857</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1857142857142857</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.8284457478005866</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.5522875816993464</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.08658170914542727</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.4224433768016472</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1822831423895254</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.6472355769230769</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.06942215088282505</v>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>135</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.05518763796909492</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.05185185185185185</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01481481481481482</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.237037037037037</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.007407407407407408</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02962962962962963</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05925925925925926</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9777777777777777</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02962962962962963</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.01481481481481482</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.007407407407407408</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.007407407407407408</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.007407407407407408</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.07792207792207789</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.01036269430051814</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7741935483870968</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.04201680672268909</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0.4871794871794872</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>39</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.2225445843168109</v>
+      </c>
+      <c r="E10" t="n">
+        <v>27.07142857142857</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.7493985126859142</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.2669400699912511</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.01921478565179353</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.00752405949256343</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.8559820647419072</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1486329833770779</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2937335958005249</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.4423665791776028</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.1451006124234471</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.2958005249343832</v>
+      </c>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1433962264150943</v>
+      </c>
+      <c r="E11" t="n">
+        <v>32.57142857142857</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.07456140350877194</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.02192982456140351</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1271929824561404</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.293859649122807</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.03947368421052632</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1798245614035088</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>